--- a/artfynd/A 21781-2026 artfynd.xlsx
+++ b/artfynd/A 21781-2026 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>428041</v>
       </c>
       <c r="B2" t="n">
-        <v>99120</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101947</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>702977.7966760934</v>
+        <v>702978</v>
       </c>
       <c r="R2" t="n">
-        <v>6668818.984878335</v>
+        <v>6668819</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2006-05-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2006-05-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -808,12 +793,7 @@
         <v>62436045</v>
       </c>
       <c r="B3" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -859,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>702996.6324412038</v>
+        <v>702997</v>
       </c>
       <c r="R3" t="n">
-        <v>6668777.058120893</v>
+        <v>6668777</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,19 +877,9 @@
           <t>2016-05-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-05-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 21781-2026 artfynd.xlsx
+++ b/artfynd/A 21781-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Floraväkteri AB-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/428041</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,8 +922,17 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62436045</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>